--- a/output/bases_limpias/Grupo_03_MODULOS/df_peip_contingencia.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_peip_contingencia.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:O120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,16 @@
           <t>ubigeo</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ugel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -545,6 +555,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -604,6 +624,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -663,6 +693,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -722,6 +762,16 @@
           <t>150111</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -781,6 +831,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -838,6 +898,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -897,6 +967,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -956,6 +1036,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1015,6 +1105,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1074,6 +1174,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1133,6 +1243,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1192,6 +1312,16 @@
           <t>150135</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1251,6 +1381,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1310,6 +1450,16 @@
           <t>150112</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1369,6 +1519,16 @@
           <t>070102</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>DRE CALLAO</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1428,6 +1588,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1485,6 +1655,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1544,6 +1724,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1603,6 +1793,16 @@
           <t>150110</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1662,6 +1862,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1721,6 +1931,16 @@
           <t>150125</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1780,6 +2000,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1839,6 +2069,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1898,6 +2138,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1957,6 +2207,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2016,6 +2276,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2075,6 +2345,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2134,6 +2414,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2193,6 +2483,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2252,6 +2552,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2311,6 +2621,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2370,6 +2690,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2429,6 +2759,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2488,6 +2828,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2547,6 +2897,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2606,6 +2966,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2665,6 +3035,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2724,6 +3104,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2781,6 +3171,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2840,6 +3240,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2899,6 +3309,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2958,6 +3378,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3017,6 +3447,16 @@
           <t>150132</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3076,6 +3516,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3135,6 +3585,16 @@
           <t>150117</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3194,6 +3654,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3253,6 +3723,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3312,6 +3792,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3371,6 +3861,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3430,6 +3930,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3489,6 +3999,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3548,6 +4068,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3607,6 +4137,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3666,6 +4206,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3725,6 +4275,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3784,6 +4344,16 @@
           <t>150118</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3843,6 +4413,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3902,6 +4482,16 @@
           <t>150103</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3961,6 +4551,16 @@
           <t>150133</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4020,6 +4620,16 @@
           <t>150128</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>UGEL 02 RÍMAC</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4079,6 +4689,16 @@
           <t>150133</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4138,6 +4758,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4197,6 +4827,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4256,6 +4896,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4315,6 +4965,16 @@
           <t>150140</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4374,6 +5034,16 @@
           <t>150140</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4433,6 +5103,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4492,6 +5172,16 @@
           <t>150108</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4551,6 +5241,16 @@
           <t>150101</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>UGEL 03 BREÑA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4610,6 +5310,16 @@
           <t>150134</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4669,6 +5379,16 @@
           <t>150134</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4728,6 +5448,16 @@
           <t>150140</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4787,6 +5517,16 @@
           <t>150140</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4846,6 +5586,16 @@
           <t>150140</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>UGEL 07 SAN BORJA</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4905,6 +5655,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4964,6 +5724,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5023,6 +5793,16 @@
           <t>150137</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5082,6 +5862,16 @@
           <t>150114</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5141,6 +5931,16 @@
           <t>150114</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>UGEL 06 ATE</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5200,6 +6000,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5259,6 +6069,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5318,6 +6138,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5377,6 +6207,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5436,6 +6276,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5495,6 +6345,16 @@
           <t>150143</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5554,6 +6414,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5613,6 +6483,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5672,6 +6552,16 @@
           <t>150142</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5731,6 +6621,16 @@
           <t>150106</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>DRE LIMA METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>UGEL 04 COMAS</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5790,6 +6690,16 @@
           <t>250301</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>DRE UCAYALI</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>UGEL PADRE ABAD</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5849,6 +6759,16 @@
           <t>120501</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>UGEL JUNÍN</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5908,6 +6828,16 @@
           <t>120901</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>UGEL CHUPACA</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5967,6 +6897,16 @@
           <t>120201</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>DRE JUNIN</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>UGEL CONCEPCIÓN</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6026,6 +6966,16 @@
           <t>150202</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6085,6 +7035,16 @@
           <t>150202</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6144,6 +7104,16 @@
           <t>140201</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GRE LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>UGEL FERREÑAFE</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6203,6 +7173,16 @@
           <t>130202</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6262,6 +7242,16 @@
           <t>061001</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>UGEL SAN MARCOS</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6321,6 +7311,16 @@
           <t>080301</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>UGEL ANTA</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6380,6 +7380,16 @@
           <t>080301</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>DRE CUSCO</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>UGEL ANTA</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6439,6 +7449,16 @@
           <t>210401</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6498,6 +7518,16 @@
           <t>211301</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>UGEL YUNGUYO</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6557,6 +7587,16 @@
           <t>211301</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>UGEL YUNGUYO</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6616,6 +7656,16 @@
           <t>210402</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6675,6 +7725,16 @@
           <t>210402</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>UGEL CHUCUITO</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6734,6 +7794,16 @@
           <t>210301</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6793,6 +7863,16 @@
           <t>210301</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>UGEL CARABAYA</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6852,6 +7932,16 @@
           <t>210201</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>UGEL AZÁNGARO</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6909,6 +7999,16 @@
       <c r="M110" t="inlineStr">
         <is>
           <t>210601</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>DRE PUNO</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>UGEL HUANCAN</t>
         </is>
       </c>
     </row>
@@ -6964,6 +8064,16 @@
           <t>200701</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>DRE PIURA</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>UGEL TALARA</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7017,6 +8127,16 @@
           <t>180303</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>DRE MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>UGEL ILO</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7070,6 +8190,16 @@
           <t>190306</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>DRE PASCO</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>UGEL PUERTO BERMÚDEZ</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7123,6 +8253,16 @@
           <t>160108</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>DRE LORETO</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>UGEL MAYNAS</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7176,6 +8316,16 @@
           <t>220701</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>UGEL PICOTA</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7229,6 +8379,16 @@
           <t>010701</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>DRE AMAZONAS</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>UGEL UTCUBAMBA</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7282,6 +8442,16 @@
           <t>060101</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>DRE CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>UGEL CAJAMARCA</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7335,6 +8505,16 @@
           <t>050110</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>DRE AYACUCHO</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>UGEL HUAMANGA</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7388,6 +8568,16 @@
           <t>130205</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>GRE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>UGEL ASCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7441,6 +8631,16 @@
           <t>150205</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>UGEL 16 BARRANCA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_peip_contingencia.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_peip_contingencia.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O120"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,11 @@
           <t>ugel</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -565,6 +570,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -634,6 +644,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -703,6 +718,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -772,6 +792,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -841,6 +866,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -908,6 +938,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -977,6 +1012,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1046,6 +1086,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1115,6 +1160,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1184,6 +1234,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1253,6 +1308,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1322,6 +1382,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1391,6 +1456,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1460,6 +1530,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1529,6 +1604,11 @@
           <t>DRE CALLAO</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1598,6 +1678,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1665,6 +1750,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1734,6 +1824,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1803,6 +1898,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1872,6 +1972,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1941,6 +2046,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2010,6 +2120,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2079,6 +2194,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2148,6 +2268,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2217,6 +2342,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2286,6 +2416,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2355,6 +2490,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2424,6 +2564,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2493,6 +2638,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2562,6 +2712,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2631,6 +2786,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2700,6 +2860,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2769,6 +2934,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2838,6 +3008,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2907,6 +3082,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2976,6 +3156,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3045,6 +3230,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3114,6 +3304,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3181,6 +3376,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3250,6 +3450,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3319,6 +3524,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3388,6 +3598,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3457,6 +3672,11 @@
           <t>UGEL 05 SAN JUAN DE LURIGANCHO</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3526,6 +3746,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3595,6 +3820,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3664,6 +3894,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3733,6 +3968,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3802,6 +4042,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3871,6 +4116,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3940,6 +4190,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4009,6 +4264,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4078,6 +4338,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4147,6 +4412,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4216,6 +4486,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4285,6 +4560,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4354,6 +4634,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4423,6 +4708,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4492,6 +4782,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4561,6 +4856,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4630,6 +4930,11 @@
           <t>UGEL 02 RÍMAC</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4699,6 +5004,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4768,6 +5078,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4837,6 +5152,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4906,6 +5226,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4975,6 +5300,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5044,6 +5374,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5113,6 +5448,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5182,6 +5522,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5251,6 +5596,11 @@
           <t>UGEL 03 BREÑA</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5320,6 +5670,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5389,6 +5744,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5458,6 +5818,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5527,6 +5892,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5596,6 +5966,11 @@
           <t>UGEL 07 SAN BORJA</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5665,6 +6040,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5734,6 +6114,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5803,6 +6188,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5872,6 +6262,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5941,6 +6336,11 @@
           <t>UGEL 06 ATE</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6010,6 +6410,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6079,6 +6484,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6148,6 +6558,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6217,6 +6632,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6286,6 +6706,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6355,6 +6780,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6424,6 +6854,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6493,6 +6928,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6562,6 +7002,11 @@
           <t>UGEL 01 SAN JUAN DE MIRAFLORES</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6631,6 +7076,11 @@
           <t>UGEL 04 COMAS</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6700,6 +7150,11 @@
           <t>UGEL PADRE ABAD</t>
         </is>
       </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6769,6 +7224,11 @@
           <t>UGEL JUNÍN</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6838,6 +7298,11 @@
           <t>UGEL CHUPACA</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6907,6 +7372,11 @@
           <t>UGEL CONCEPCIÓN</t>
         </is>
       </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6976,6 +7446,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7045,6 +7520,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7114,6 +7594,11 @@
           <t>UGEL FERREÑAFE</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7183,6 +7668,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7252,6 +7742,11 @@
           <t>UGEL SAN MARCOS</t>
         </is>
       </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7321,6 +7816,11 @@
           <t>UGEL ANTA</t>
         </is>
       </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7390,6 +7890,11 @@
           <t>UGEL ANTA</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7459,6 +7964,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7528,6 +8038,11 @@
           <t>UGEL YUNGUYO</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7597,6 +8112,11 @@
           <t>UGEL YUNGUYO</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7666,6 +8186,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7735,6 +8260,11 @@
           <t>UGEL CHUCUITO</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7804,6 +8334,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7873,6 +8408,11 @@
           <t>UGEL CARABAYA</t>
         </is>
       </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7942,6 +8482,11 @@
           <t>UGEL AZÁNGARO</t>
         </is>
       </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8009,6 +8554,11 @@
       <c r="O110" t="inlineStr">
         <is>
           <t>UGEL HUANCAN</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>PEIP</t>
         </is>
       </c>
     </row>
@@ -8074,6 +8624,11 @@
           <t>UGEL TALARA</t>
         </is>
       </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8137,6 +8692,11 @@
           <t>UGEL ILO</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8200,6 +8760,11 @@
           <t>UGEL PUERTO BERMÚDEZ</t>
         </is>
       </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8263,6 +8828,11 @@
           <t>UGEL MAYNAS</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8326,6 +8896,11 @@
           <t>UGEL PICOTA</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8389,6 +8964,11 @@
           <t>UGEL UTCUBAMBA</t>
         </is>
       </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8452,6 +9032,11 @@
           <t>UGEL CAJAMARCA</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8515,6 +9100,11 @@
           <t>UGEL HUAMANGA</t>
         </is>
       </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8578,6 +9168,11 @@
           <t>UGEL ASCOPE</t>
         </is>
       </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -8641,6 +9236,11 @@
           <t>UGEL 16 BARRANCA</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>PEIP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_peip_contingencia.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_peip_contingencia.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P120"/>
+  <dimension ref="A1:R120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,16 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>fuente</t>
         </is>
       </c>
@@ -572,6 +582,16 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN/JORGE BASADRE GROHMANN</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -646,6 +666,16 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>SAN FELIPE/SAN FELIPE</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -720,6 +750,16 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>SAN FELIPE/SAN FELIPE</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -794,6 +834,16 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE/0085 JOSE DE LA TORRE UGARTE</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -868,6 +918,16 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>0035 NUESTRA SEÑORA DE LA VISITACION/0035 NUESTRA SEÑORA DE LA VISITACION/0035 NUESTRA SEÑORA DE LA VISITACION</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -940,6 +1000,16 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>2028 PERUANO BRITANICO/2028 PERUANO BRITANICO</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1014,6 +1084,16 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>3094-1 J. WILLIAM FULBRIGHT/09 J. WILLIAM FULBRIGHT</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1088,6 +1168,16 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>3048 SANTIAGO ANTUNEZ DE MAYOLO/3048 SANTIAGO ANTUNEZ DE MAYOLO/3048 SANTIAGO ANTUNEZ DE MAYOLO</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1162,6 +1252,16 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>3048 SANTIAGO ANTUNEZ DE MAYOLO/3048 SANTIAGO ANTUNEZ DE MAYOLO/3048 SANTIAGO ANTUNEZ DE MAYOLO</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1236,6 +1336,16 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>3048 SANTIAGO ANTUNEZ DE MAYOLO/3048 SANTIAGO ANTUNEZ DE MAYOLO/3048 SANTIAGO ANTUNEZ DE MAYOLO</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1310,6 +1420,16 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>2096 PERU JAPON</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1384,6 +1504,16 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>2029 SIMON BOLIVAR/2029 SIMON BOLIVAR/2029 SIMON BOLIVAR/2029 SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1458,6 +1588,16 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>3094-1 J. WILLIAM FULBRIGHT/09 J. WILLIAM FULBRIGHT</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1532,6 +1672,16 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>3049 IMPERIO DEL TAHUANTINSUYO/3049 IMPERIO DEL TAHUANTINSUYO/3049 IMPERIO DEL TAHUANTINSUYO</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1606,6 +1756,16 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>GENERAL PRADO/GENERAL PRADO/GENERAL PRADO/GENERAL PRADO</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1680,6 +1840,16 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>3058 VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1752,6 +1922,16 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>2051 - EL PROGRESO/2051 - EL PROGRESO</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1826,6 +2006,16 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>2100 JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1900,6 +2090,16 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>3065 VIRGEN DEL CARMEN/3065 VIRGEN DEL CARMEN/3065 VIRGEN DEL CARMEN</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -1974,6 +2174,16 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>8184 SAN BENITO/8184 SAN BENITO/8184 SAN BENITO</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2048,6 +2258,16 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
+          <t>3088 VISTA ALEGRE/3088 VISTA ALEGRE</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2122,6 +2342,16 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
+          <t>1190 FELIPE HUAMAN POMA DE AYALA/1190 FELIPE HUAMAN POMA DE AYALA</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2196,6 +2426,16 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
+          <t>0171 01 JUAN VELASCO ALVARADO/0171-01 JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2270,6 +2510,16 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
+          <t>0171 01 JUAN VELASCO ALVARADO/0171-01 JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2344,6 +2594,16 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
+          <t>FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2418,6 +2678,16 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
+          <t>FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2492,6 +2762,16 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
+          <t>FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES/FRANCISCO BOLOGNESI CERVANTES</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2566,6 +2846,16 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
+          <t>142 MARTIR DANIEL ALCIDES CARRION/142 MARTIR DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2640,6 +2930,16 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
+          <t>142 MARTIR DANIEL ALCIDES CARRION/142 MARTIR DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2714,6 +3014,16 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
+          <t>159 GLORIOSO 10 DE OCTUBRE/159 GLORIOSO 10 DE OCTUBRE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2788,6 +3098,16 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
+          <t>RAMIRO PRIALE PRIALE</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2862,6 +3182,16 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
+          <t>166 KAROL WOJTYLA/166 KAROL WOJTYLA</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -2936,6 +3266,16 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
+          <t>166 KAROL WOJTYLA/166 KAROL WOJTYLA</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3010,6 +3350,16 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
+          <t>0132 TORIBIO DE LUZURIAGA Y MEJIA/0132 TORIBIO DE LUZURIAGA Y MEJIA/0132 TORIBIO DE LUZURIAGA Y MEJIA</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3084,6 +3434,16 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
+          <t>0132 TORIBIO DE LUZURIAGA Y MEJIA/0132 TORIBIO DE LUZURIAGA Y MEJIA/0132 TORIBIO DE LUZURIAGA Y MEJIA</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3158,6 +3518,16 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
+          <t>0132 TORIBIO DE LUZURIAGA Y MEJIA/0132 TORIBIO DE LUZURIAGA Y MEJIA/0132 TORIBIO DE LUZURIAGA Y MEJIA</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3232,6 +3602,16 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
+          <t>109 INCA MANCO CAPAC/109 INCA MANCO CAPAC/109 INCA MANCO CAPAC/109 INCA MANCO CAPAC</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3306,6 +3686,16 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
+          <t>1179 TOMAS ALVA EDISON/1179 TOMAS ALVA EDISON/1179 TOMAS ALVA EDISON</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3378,6 +3768,16 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
+          <t>100/100/100</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3452,6 +3852,16 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
+          <t>145 INDEPENDENCIA AMERICANA/145 INDEPENDENCIA AMERICANA/145 INDEPENDENCIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3526,6 +3936,16 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
+          <t>139 GRAN AMAUTA MARIATEGUI/139 GRAN AMAUTA MARIATEGUI</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3600,6 +4020,16 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
+          <t>126 JAVIER PEREZ DE CUELLAR/126 JAVIER PEREZ DE CUELLAR</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3674,6 +4104,16 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
+          <t>163 TENIENTE CORONEL EP NESTOR ESCUDERO OTERO/163 TENIENTE CORONEL EP NESTOR ESCUDERO OTERO</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3748,6 +4188,16 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
+          <t>3080 PERU - CANADA/3080 PERU - CANADA</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3822,6 +4272,16 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
+          <t>3080 PERU - CANADA/3080 PERU - CANADA</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3896,6 +4356,16 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
+          <t>1268 GUSTAVO MOHME LLONA/1268 GUSTAVO MOHME LLONA</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -3970,6 +4440,16 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
+          <t>1268 GUSTAVO MOHME LLONA/1268 GUSTAVO MOHME LLONA</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4044,6 +4524,16 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
+          <t>1268 GUSTAVO MOHME LLONA/1268 GUSTAVO MOHME LLONA</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4118,6 +4608,16 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALEZ PRADA</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4192,6 +4692,16 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALEZ PRADA</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4266,6 +4776,16 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALEZ PRADA</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4340,6 +4860,16 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
+          <t>MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALES PRADA/MANUEL GONZALEZ PRADA/MANUEL GONZALEZ PRADA</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4414,6 +4944,16 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
+          <t>0034 PERUANO FINLANDES</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4488,6 +5028,16 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
+          <t>1209 MARISCAL TORIBIO DE LUZURIAGA/1209 MARISCAL TORIBIO DE LUZURIAGA</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4562,6 +5112,16 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
+          <t>1267/1267/1267</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4636,6 +5196,16 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
+          <t>1267/1267/1267</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4710,6 +5280,16 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
+          <t>1255 WALTER PEÑALOZA RAMELLA/1255 WALTER PEÑALOZA RAMELLA</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4784,6 +5364,16 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
+          <t>VICTOR RAUL HAYA DE LA TORRE/046 VICTOR RAUL HAYA DE LA TORRE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4858,6 +5448,16 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
+          <t>7207 MARISCAL RAMON CASTILLA/7207 MARISCAL RAMON CASTILLA</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -4932,6 +5532,16 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
+          <t>2099 PATRICIA ROSA MERINO/2099 PATRICIA ROSA MERINO</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5006,6 +5616,16 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
+          <t>JAVIER HERAUD/JAVIER HERAUD</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5080,6 +5700,16 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
+          <t>101 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5154,6 +5784,16 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
+          <t>101 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5228,6 +5868,16 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
+          <t>101 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR/1166 LIBERTADOR SIMON BOLIVAR</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5302,6 +5952,16 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
+          <t>7086 LOS PRECURSORES/7086 LOS PRECURSORES/7086 LOS PRECURSORES</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5376,6 +6036,16 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
+          <t>7086 LOS PRECURSORES/7086 LOS PRECURSORES/7086 LOS PRECURSORES</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5450,6 +6120,16 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
+          <t>6094 SANTA ROSA/6094 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5524,6 +6204,16 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
+          <t>6094 SANTA ROSA/6094 SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5598,6 +6288,16 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
+          <t>1124 JOSE MARTI/1124 JOSE MARTI</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5672,6 +6372,16 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
+          <t>0083 SAN JUAN MACIAS/0083 SAN JUAN MACIAS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5746,6 +6456,16 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
+          <t>0083 SAN JUAN MACIAS/0083 SAN JUAN MACIAS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5820,6 +6540,16 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
+          <t>6082 LOS PROCERES/6082 LOS PROCERES</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5894,6 +6624,16 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
+          <t>6082 LOS PROCERES/6082 LOS PROCERES</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -5968,6 +6708,16 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
+          <t>6082 LOS PROCERES/6082 LOS PROCERES</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6042,6 +6792,16 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
+          <t>1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6116,6 +6876,16 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
+          <t>1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6190,6 +6960,16 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
+          <t>1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO/1221 MARIA PARADO DE BELLIDO</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6264,6 +7044,16 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
+          <t>1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6338,6 +7128,16 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
+          <t>1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA/1235 UNION LATINOAMERICANA</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6412,6 +7212,16 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
+          <t>6064 FRANCISCO BOLOGNESI/6064 FRANCISCO BOLOGNESI/6064 FRANCISCO BOLOGNESI</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6486,6 +7296,16 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
+          <t>6011 SANTISIMA VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6560,6 +7380,16 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
+          <t>REPUBLICA DEL ECUADOR/REPUBLICA DEL ECUADOR</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6634,6 +7464,16 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
+          <t>6152 STELLA MARIS/6152 STELLA MARIS/6152 STELLA MARIS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6708,6 +7548,16 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
+          <t>FE Y ALEGRIA 23/FE Y ALEGRIA 23/FE Y ALEGRIA 23</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6782,6 +7632,16 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
+          <t>FE Y ALEGRIA 24/FE Y ALEGRIA 24</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6856,6 +7716,16 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
+          <t>6048 JORGE BASADRE/6048 JORGE BASADRE/6048 JORGE BASADRE</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -6930,6 +7800,16 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
+          <t>7228 PERUANO CANADIENSE/7228 PERUANO CANADIENSE</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7004,6 +7884,16 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
+          <t>7228 PERUANO CANADIENSE/7228 PERUANO CANADIENSE</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7078,6 +7968,16 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
+          <t>2025 - PAPA LEON XIV</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7152,6 +8052,16 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
+          <t>FERNANDO CARBAJAL/FERNANDO CARBAJAL/FERNANDO CARBAJAL</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7226,6 +8136,16 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
+          <t>SEIS DE AGOSTO/SEIS DE AGOSTO</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7300,6 +8220,16 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7374,6 +8304,16 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
+          <t>9 DE JULIO/9 DE JULIO</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7448,6 +8388,16 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
+          <t>21578</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7522,6 +8472,16 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
+          <t>21578</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7596,6 +8556,16 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
+          <t>SANTA LUCIA</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7670,6 +8640,16 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
+          <t>SANTO DOMINGO DE GUZMAN/SANTO DOMINGO DE GUZMAN</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7744,6 +8724,16 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
+          <t>SAN MARCOS/SAN MARCOS/SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7818,6 +8808,16 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
+          <t>AGUSTIN GAMARRA/AGUSTIN GAMARRA/AGUSTIN GAMARRA</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7892,6 +8892,16 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
+          <t>AGUSTIN GAMARRA/AGUSTIN GAMARRA/AGUSTIN GAMARRA</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -7966,6 +8976,16 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
+          <t>TELESFORO CATACORA/TELESFORO CATACORA/TELESFORO CATACORA</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8040,6 +9060,16 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
+          <t>301 JOSE GALVEZ/JOSE GALVEZ</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8114,6 +9144,16 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
+          <t>301 JOSE GALVEZ/JOSE GALVEZ</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8188,6 +9228,16 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
+          <t>TAWANTINSUYO/TAWANTINSUYO</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8262,6 +9312,16 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
+          <t>TAWANTINSUYO/TAWANTINSUYO</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8336,6 +9396,16 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
+          <t>73002 GLORIOSO 821</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8410,6 +9480,16 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
+          <t>73002 GLORIOSO 821</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8484,6 +9564,16 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
+          <t>PEDRO VILCAPAZA</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8557,6 +9647,16 @@
         </is>
       </c>
       <c r="P110" t="inlineStr">
+        <is>
+          <t>VARONES</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
         <is>
           <t>PEIP</t>
         </is>
@@ -8626,6 +9726,16 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
+          <t>EMBLEMATICA 15513/EMBLEMATICA 15513/EMBLEMATICA 15513</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8694,6 +9804,16 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
+          <t>AMERICO GARIBALDI GHERSI/AMERICO GARIBALDI GHERSI</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8762,6 +9882,16 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
+          <t>34618 REMIGIO MORALES BERMUDEZ/34618 REMIGIO MORALES BERMUDEZ/34618 REMIGIO MORALES BERMUDEZ</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8830,6 +9960,16 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
+          <t>60052 GENERALISIMO JOSE DE SAN MARTIN/60052 GENERALISIMO JOSE DE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8898,6 +10038,16 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
+          <t>ALBERTO LEVEAU GARCIA/ALBERTO LEVEAU GARCIA/ALBERTO LEVEAU GARCIA</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -8966,6 +10116,16 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
+          <t>JORGE CHAVEZ BERTNELLI</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -9034,6 +10194,16 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
+          <t>RAFAEL LOAYZA GUEVARA</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -9102,6 +10272,16 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
+          <t>SAN JUAN/SAN JUAN/SAN JUAN</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -9170,6 +10350,16 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
+          <t>LEONCIO PRADO/LEONCIO PRADO/LEONCIO PRADO</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>
@@ -9238,6 +10428,16 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
+          <t>20790</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
           <t>PEIP</t>
         </is>
       </c>

--- a/output/bases_limpias/Grupo_03_MODULOS/df_peip_contingencia.xlsx
+++ b/output/bases_limpias/Grupo_03_MODULOS/df_peip_contingencia.xlsx
@@ -423,42 +423,42 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>N°</t>
+          <t>n</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CUI</t>
+          <t>cui</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Código Local</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Nombre del PEIP</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Tipo de sistema modular</t>
+          <t>tipo_de_sistema_modular</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Cantidad de módulos PEIP</t>
+          <t>cantidad_de_modulos_peip</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Cantidad de módulos PRONIED</t>
+          <t>cantidad_de_modulos_pronied</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Año de instalación de los módulos</t>
+          <t>ano_de_instalacion_de_los_modulos</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>nombre_ie</t>
+          <t>nombre_ie_2</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
